--- a/output/pdf_financials_xlsx/HML.xlsx
+++ b/output/pdf_financials_xlsx/HML.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.306092</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.7429829999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.578264</v>
       </c>
     </row>
     <row r="93">
@@ -3049,7 +3049,11 @@
           <t>Reserves (Notes 8 and 9)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3287,7 +3291,11 @@
           <t>Reserves (Notes 8 and 9)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.306092</v>
       </c>

--- a/output/pdf_financials_xlsx/HML.xlsx
+++ b/output/pdf_financials_xlsx/HML.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.172213</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.558277</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.209669</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.172213</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.558277</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.209669</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.232665</v>
+        <v>0.060452</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.7420949999999999</v>
+        <v>0.183818</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.386958</v>
+        <v>0.177289</v>
       </c>
     </row>
     <row r="49">
@@ -2419,13 +2419,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.065163</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.160535</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.304511</v>
       </c>
     </row>
     <row r="125">
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.065163</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.160535</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.304511</v>
       </c>
     </row>
     <row r="126">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3937,7 +3937,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
         <v>-0.065163</v>
       </c>

--- a/output/pdf_financials_xlsx/HML.xlsx
+++ b/output/pdf_financials_xlsx/HML.xlsx
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="68">
@@ -1558,13 +1558,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.07190199999999999</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.170677</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.12322</v>
       </c>
     </row>
     <row r="71">
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.07190199999999999</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.170677</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.12322</v>
       </c>
     </row>
     <row r="72">
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.07190199999999999</v>
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.170677</v>
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.149967</v>
+        <v>0.026747</v>
       </c>
     </row>
     <row r="76">
@@ -1717,20 +1717,14 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.3966372276987406</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.2740425682228345</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>-0.3642038619442137</v>
       </c>
     </row>
     <row r="81">
@@ -2051,13 +2045,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.006395</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.07723099999999999</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.010759</v>
       </c>
     </row>
     <row r="102">
@@ -2131,13 +2125,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.630454</v>
+        <v>0.636849</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.122054</v>
+        <v>0.199285</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>1.083448</v>
+        <v>1.072689</v>
       </c>
     </row>
     <row r="107">
@@ -2896,7 +2890,11 @@
           <t>Lease liabilities (Note 7)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>0.07190199999999999</v>
       </c>
@@ -3728,7 +3726,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>0.006395</v>
       </c>
@@ -3848,7 +3850,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>1.3013</v>
       </c>
